--- a/quizzes/045_matchmaking_quiz--quizzes.xlsx
+++ b/quizzes/045_matchmaking_quiz--quizzes.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1159,12 +1159,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'single'}</t>
+          <t>single</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'Single'}</t>
+          <t>Single</t>
         </is>
       </c>
     </row>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'in_a_relationship'}</t>
+          <t>in_a_relationship</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'In a relationship'}</t>
+          <t>In a relationship</t>
         </is>
       </c>
     </row>
@@ -1193,12 +1193,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'in_a_relationship_and_looking_to_start_a_new_relationship'}</t>
+          <t>in_a_relationship_and_looking_to_start_a_new_relationship</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'In a relationship and looking to start a new relationship'}</t>
+          <t>In a relationship and looking to start a new relationship</t>
         </is>
       </c>
     </row>
@@ -1210,12 +1210,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'friendship'}</t>
+          <t>friendship</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'Friendship'}</t>
+          <t>Friendship</t>
         </is>
       </c>
     </row>
@@ -1227,12 +1227,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'casual_relationship'}</t>
+          <t>casual_relationship</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'Casual Relationship'}</t>
+          <t>Casual Relationship</t>
         </is>
       </c>
     </row>
@@ -1244,12 +1244,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'long-term_partnership'}</t>
+          <t>long-term_partnership</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'Long-Term Partnership'}</t>
+          <t>Long-Term Partnership</t>
         </is>
       </c>
     </row>
@@ -1261,12 +1261,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_4,_'value':_'serious_relationship'}</t>
+          <t>serious_relationship</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 4, 'value': 'Serious Relationship'}</t>
+          <t>Serious Relationship</t>
         </is>
       </c>
     </row>
@@ -1278,12 +1278,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'age'}</t>
+          <t>age</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'Age'}</t>
+          <t>Age</t>
         </is>
       </c>
     </row>
@@ -1295,12 +1295,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'interests'}</t>
+          <t>interests</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'Interests'}</t>
+          <t>Interests</t>
         </is>
       </c>
     </row>
@@ -1312,12 +1312,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'personality'}</t>
+          <t>personality</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'Personality'}</t>
+          <t>Personality</t>
         </is>
       </c>
     </row>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_4,_'value':_'lifestyle'}</t>
+          <t>lifestyle</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 4, 'value': 'Lifestyle'}</t>
+          <t>Lifestyle</t>
         </is>
       </c>
     </row>
@@ -1346,12 +1346,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'family'}</t>
+          <t>family</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'Family'}</t>
+          <t>Family</t>
         </is>
       </c>
     </row>
@@ -1363,12 +1363,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'health'}</t>
+          <t>health</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'Health'}</t>
+          <t>Health</t>
         </is>
       </c>
     </row>
@@ -1380,12 +1380,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'happiness'}</t>
+          <t>happiness</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'Happiness'}</t>
+          <t>Happiness</t>
         </is>
       </c>
     </row>
@@ -1397,12 +1397,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_4,_'value':_'wealth'}</t>
+          <t>wealth</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 4, 'value': 'Wealth'}</t>
+          <t>Wealth</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1431,12 +1431,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1448,12 +1448,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'high_school'}</t>
+          <t>high_school</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'High School'}</t>
+          <t>High School</t>
         </is>
       </c>
     </row>
@@ -1465,12 +1465,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'college'}</t>
+          <t>college</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'College'}</t>
+          <t>College</t>
         </is>
       </c>
     </row>
@@ -1482,12 +1482,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'university'}</t>
+          <t>university</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'University'}</t>
+          <t>University</t>
         </is>
       </c>
     </row>
@@ -1499,12 +1499,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_4,_'value':_'doctoral_degree_or_higher'}</t>
+          <t>doctoral_degree_or_higher</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 4, 'value': 'Doctoral degree or higher'}</t>
+          <t>Doctoral degree or higher</t>
         </is>
       </c>
     </row>
@@ -1516,12 +1516,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'hiking'}</t>
+          <t>hiking</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'Hiking'}</t>
+          <t>Hiking</t>
         </is>
       </c>
     </row>
@@ -1533,12 +1533,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'reading'}</t>
+          <t>reading</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'Reading'}</t>
+          <t>Reading</t>
         </is>
       </c>
     </row>
@@ -1550,12 +1550,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'traveling'}</t>
+          <t>traveling</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'Traveling'}</t>
+          <t>Traveling</t>
         </is>
       </c>
     </row>
@@ -1567,12 +1567,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_4,_'value':_'sports'}</t>
+          <t>sports</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 4, 'value': 'Sports'}</t>
+          <t>Sports</t>
         </is>
       </c>
     </row>
